--- a/hourly datasets/cap_gen_year13final.xlsx
+++ b/hourly datasets/cap_gen_year13final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09938754597967438</v>
+        <v>0.09838588330122627</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09544247632357654</v>
+        <v>0.09243899126926371</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1948300223032509</v>
+        <v>0.19082487457049</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07433551145063542</v>
+        <v>0.06783658484210676</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1737230574303098</v>
+        <v>0.166222468143333</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04606018388745416</v>
+        <v>0.0341644918423659</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +539,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1454477298671285</v>
+        <v>0.1325503751435922</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06073887638649635</v>
+        <v>0.04962748051893594</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +557,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1601264223661707</v>
+        <v>0.1480133638201622</v>
       </c>
     </row>
     <row r="7">
@@ -567,15 +567,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05558531632287125</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>0.03928870136896329</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.001428395492628408</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5.521518619193079</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.006165813426167861</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03648819120093257</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.04208921153699407</v>
+      </c>
       <c r="H7" t="n">
-        <v>0.1549728623025456</v>
+        <v>0.1376745846701896</v>
       </c>
     </row>
     <row r="8">
@@ -585,25 +595,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03768428929135112</v>
+        <v>0.006493849564255303</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002056094966887085</v>
+        <v>0.0004098325592733876</v>
       </c>
       <c r="D8" t="n">
-        <v>4.610602075245989</v>
+        <v>1.912616663202308</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0145225967495337</v>
+        <v>0.007277047137359598</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03365153501609233</v>
+        <v>0.005688801297783905</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04171704356661073</v>
+        <v>0.007298897830726649</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1370718352710255</v>
+        <v>0.1048797328654816</v>
       </c>
     </row>
     <row r="9">
@@ -613,15 +623,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03702959467894879</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+        <v>0.003575937101282349</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.001244050471326555</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.524880007330657</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.008773866488276091</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.001131307300303855</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.006020566902260867</v>
+      </c>
       <c r="H9" t="n">
-        <v>0.1364171406586231</v>
+        <v>0.1019618204025086</v>
       </c>
     </row>
     <row r="10">
@@ -631,25 +651,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.03750736443914262</v>
+        <v>0.00397085466038251</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002441190054921404</v>
+        <v>0.000875539359265155</v>
       </c>
       <c r="D10" t="n">
-        <v>4.55487105918922</v>
+        <v>1.232649415934603</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00892760710090874</v>
+        <v>0.005433284990461768</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03271774425642111</v>
+        <v>0.002250583250542776</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04229698462186376</v>
+        <v>0.005691126070222226</v>
       </c>
       <c r="H10" t="n">
-        <v>0.136894910418817</v>
+        <v>0.1023567379616088</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +679,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0299333419793639</v>
+        <v>0.02809190705169527</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -667,7 +687,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1293208879590383</v>
+        <v>0.1264777903529215</v>
       </c>
     </row>
     <row r="12">
@@ -677,7 +697,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05235207103284203</v>
+        <v>0.04929621084129866</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -685,7 +705,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1517396170125164</v>
+        <v>0.1476820941425249</v>
       </c>
     </row>
     <row r="13">
@@ -695,7 +715,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06459953424568558</v>
+        <v>0.06213948076942288</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -703,7 +723,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.16398708022536</v>
+        <v>0.1605253640706492</v>
       </c>
     </row>
     <row r="14">
@@ -713,7 +733,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07541470999723525</v>
+        <v>0.07269881530493509</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -721,7 +741,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1748022559769096</v>
+        <v>0.1710846986061614</v>
       </c>
     </row>
     <row r="15">
@@ -731,7 +751,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08077247944632321</v>
+        <v>0.0765398871024441</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -739,7 +759,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1801600254259976</v>
+        <v>0.1749257704036704</v>
       </c>
     </row>
     <row r="16">
@@ -749,7 +769,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08348292184851812</v>
+        <v>0.079796918219929</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -757,7 +777,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1828704678281925</v>
+        <v>0.1781828015211553</v>
       </c>
     </row>
     <row r="17">
@@ -767,7 +787,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08625249812131089</v>
+        <v>0.08246904577365693</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -775,7 +795,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1856400441009853</v>
+        <v>0.1808549290748832</v>
       </c>
     </row>
     <row r="18">
@@ -785,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09938754597967438</v>
+        <v>-0.09838588330122627</v>
       </c>
       <c r="C18" t="n">
-        <v>0.008653689853673477</v>
+        <v>0.007912478261805548</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.86719455148055</v>
+        <v>-19.37902157745466</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0246845553515376</v>
+        <v>0.02203389742351249</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1164063896228987</v>
+        <v>-0.1139408608977274</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08236870233644973</v>
+        <v>-0.08283090570472514</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -813,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09066174891765244</v>
+        <v>0.08725255884178368</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -821,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1900492948973268</v>
+        <v>0.18563844214301</v>
       </c>
     </row>
     <row r="20">
@@ -831,7 +851,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09232087629706269</v>
+        <v>0.08869424987457243</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -839,7 +859,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1917084222767371</v>
+        <v>0.1870801331757987</v>
       </c>
     </row>
     <row r="21">
@@ -849,7 +869,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09727129600694094</v>
+        <v>0.09337813705766983</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -857,7 +877,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1966588419866153</v>
+        <v>0.1917640203588961</v>
       </c>
     </row>
     <row r="22">
@@ -867,7 +887,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1000947009958603</v>
+        <v>0.09680776454347796</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -875,7 +895,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1994822469755347</v>
+        <v>0.1951936478447042</v>
       </c>
     </row>
     <row r="23">
@@ -885,25 +905,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.103999561416143</v>
+        <v>0.1011943530032605</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007785622198110591</v>
+        <v>0.007360777304507381</v>
       </c>
       <c r="D23" t="n">
-        <v>-323436960025.2491</v>
+        <v>-320936973120.3779</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04744812292787406</v>
+        <v>0.04858762411570535</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08869425653373132</v>
+        <v>0.08671984857694275</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1193048662985546</v>
+        <v>0.1156688574295779</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2033871073958173</v>
+        <v>0.1995802363044868</v>
       </c>
     </row>
     <row r="24">
@@ -913,7 +933,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1068487404761665</v>
+        <v>0.1042209776396423</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -921,7 +941,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2062362864558409</v>
+        <v>0.2026068609408686</v>
       </c>
     </row>
     <row r="25">
@@ -931,25 +951,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1091724292302566</v>
+        <v>0.1065634717375542</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007745187477226081</v>
+        <v>0.007322077872722325</v>
       </c>
       <c r="D25" t="n">
-        <v>25.64992793640603</v>
+        <v>25.87559226569</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04992955927607987</v>
+        <v>0.04632825638865</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09394820866560222</v>
+        <v>0.09217065190357181</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1243966497949112</v>
+        <v>0.1209562915715369</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2085599752099309</v>
+        <v>0.2049493550387804</v>
       </c>
     </row>
     <row r="26">
@@ -959,25 +979,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1093807751548355</v>
+        <v>0.1078920291343967</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007758347567464143</v>
+        <v>0.007374014222839818</v>
       </c>
       <c r="D26" t="n">
-        <v>-111759430900.8102</v>
+        <v>-111123772321.5228</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05997937961130436</v>
+        <v>0.05614965926113593</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09413546175669202</v>
+        <v>0.09340131711886501</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1246260885529791</v>
+        <v>0.122382741149928</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2087683211345099</v>
+        <v>0.2062779124356229</v>
       </c>
     </row>
     <row r="27">
@@ -987,7 +1007,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1129574129246157</v>
+        <v>0.1103345163489635</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -995,7 +1015,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.2123449589042901</v>
+        <v>0.2087203996501898</v>
       </c>
     </row>
     <row r="28">
@@ -1005,25 +1025,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1076206129339424</v>
+        <v>0.1045415050733467</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007314701122807652</v>
+        <v>0.0066833249351691</v>
       </c>
       <c r="D28" t="n">
-        <v>22.52232618684381</v>
+        <v>22.90784004910377</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08773815096072336</v>
+        <v>0.08255517700603007</v>
       </c>
       <c r="F28" t="n">
-        <v>0.09325684945791586</v>
+        <v>0.0914169604953203</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1219843764099697</v>
+        <v>0.117666049651373</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2070081589136168</v>
+        <v>0.202927388374573</v>
       </c>
     </row>
     <row r="29">
@@ -1033,25 +1053,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.04175810814375928</v>
+        <v>0.005583433311098755</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002461833108853095</v>
+        <v>0.0008485499072841625</v>
       </c>
       <c r="D29" t="n">
-        <v>4.917267414069542</v>
+        <v>1.294361354548581</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0105151434110451</v>
+        <v>0.007992271573822686</v>
       </c>
       <c r="F29" t="n">
-        <v>0.03692382100225468</v>
+        <v>0.003908741157821331</v>
       </c>
       <c r="G29" t="n">
-        <v>0.04659239528526291</v>
+        <v>0.007258125464376035</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1411456541234337</v>
+        <v>0.103969316612325</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year13final.xlsx
+++ b/hourly datasets/cap_gen_year13final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2268610183673885</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.09838588330122627</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09917050166400887</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.09243899126926371</v>
+        <v>0.3904080265853935</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.19082487457049</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2627175098820139</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06783658484210676</v>
+        <v>0.3850830882772089</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.166222468143333</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2573925715738292</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +545,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0341644918423659</v>
+        <v>0.3811481838305575</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +553,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1325503751435922</v>
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2534576671271779</v>
       </c>
     </row>
     <row r="6">
@@ -549,7 +566,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04962748051893594</v>
+        <v>0.3743371743137356</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -557,7 +574,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1480133638201622</v>
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.246646657610356</v>
       </c>
     </row>
     <row r="7">
@@ -567,25 +587,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03928870136896329</v>
+        <v>0.4935818301448788</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001428395492628408</v>
+        <v>0.009853918201110921</v>
       </c>
       <c r="D7" t="n">
-        <v>5.521518619193079</v>
+        <v>31.37825883803286</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006165813426167861</v>
+        <v>0.006511528549783261</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03648819120093257</v>
+        <v>0.2812137318042235</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04208921153699407</v>
+        <v>0.3198473956347376</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1376745846701896</v>
+        <v>22</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3658913134414992</v>
       </c>
     </row>
     <row r="8">
@@ -595,25 +618,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.006493849564255303</v>
+        <v>0.4917564579548573</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004098325592733876</v>
+        <v>0.003870910902795488</v>
       </c>
       <c r="D8" t="n">
-        <v>1.912616663202308</v>
+        <v>56.20031180925972</v>
       </c>
       <c r="E8" t="n">
-        <v>0.007277047137359598</v>
+        <v>0.07793245438481573</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005688801297783905</v>
+        <v>0.2092843620656558</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007298897830726649</v>
+        <v>0.2244635709601178</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1048797328654816</v>
+        <v>181</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3640659412514776</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +649,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003575937101282349</v>
+        <v>0.3221961658206423</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001244050471326555</v>
+        <v>0.006348658487079009</v>
       </c>
       <c r="D9" t="n">
-        <v>1.524880007330657</v>
+        <v>-0.3977409575543784</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008773866488276091</v>
+        <v>0.0125872882988842</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001131307300303855</v>
+        <v>-0.02267875571754672</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006020566902260867</v>
+        <v>0.002231064421933273</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1019618204025086</v>
+        <v>141</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1945056491172626</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +680,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00397085466038251</v>
+        <v>0.3245275275508935</v>
       </c>
       <c r="C10" t="n">
-        <v>0.000875539359265155</v>
+        <v>0.002545878857231487</v>
       </c>
       <c r="D10" t="n">
-        <v>1.232649415934603</v>
+        <v>-9.624574300290359</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005433284990461768</v>
+        <v>0.00705080198140634</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002250583250542776</v>
+        <v>-0.01174488896515844</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005691126070222226</v>
+        <v>-0.001752018423009801</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1023567379616088</v>
+        <v>141</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1968370108475139</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +711,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02809190705169527</v>
+        <v>0.2794439448177983</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +719,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1264777903529215</v>
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1517534281144186</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04929621084129866</v>
+        <v>0.2975342602144749</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +740,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1476820941425249</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1698437435110952</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +753,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06213948076942288</v>
+        <v>0.3144189843252841</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +761,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1605253640706492</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1867284676219045</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +774,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07269881530493509</v>
+        <v>0.3252252870607896</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +782,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1710846986061614</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1975347703574099</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0765398871024441</v>
+        <v>0.3323704243689287</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +803,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1749257704036704</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2046799076655491</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +816,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.079796918219929</v>
+        <v>0.3367096714690959</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +824,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1781828015211553</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2090191547657162</v>
       </c>
     </row>
     <row r="17">
@@ -787,7 +837,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08246904577365693</v>
+        <v>0.3407138432541739</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -795,7 +845,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1808549290748832</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2130233265507942</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.09838588330122627</v>
+        <v>0.1276905167033796</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007912478261805548</v>
+        <v>0.008569120494181914</v>
       </c>
       <c r="D18" t="n">
-        <v>-19.37902157745466</v>
+        <v>-19.91384980661291</v>
       </c>
       <c r="E18" t="n">
-        <v>0.02203389742351249</v>
+        <v>0.02213881923807912</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1139408608977274</v>
+        <v>-0.1203279451834354</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08283090570472514</v>
+        <v>-0.08663706339168568</v>
       </c>
       <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08725255884178368</v>
+        <v>0.3434870111029009</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.18563844214301</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2157964943995212</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +910,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.08869424987457243</v>
+        <v>0.3470456167283502</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +918,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1870801331757987</v>
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2193551000249706</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +931,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.09337813705766983</v>
+        <v>0.3524787430636405</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +939,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1917640203588961</v>
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2247882263602609</v>
       </c>
     </row>
     <row r="22">
@@ -887,7 +952,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.09680776454347796</v>
+        <v>0.3571548293590831</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
@@ -895,7 +960,10 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.1951936478447042</v>
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2294643126557035</v>
       </c>
     </row>
     <row r="23">
@@ -905,25 +973,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1011943530032605</v>
+        <v>0.3633387459468864</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007360777304507381</v>
+        <v>0.007366582333927339</v>
       </c>
       <c r="D23" t="n">
-        <v>-320936973120.3779</v>
+        <v>-321190077988.7693</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04858762411570535</v>
+        <v>0.04862594243125401</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08671984857694275</v>
+        <v>0.08678823962471637</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1156688574295779</v>
+        <v>0.1157600789259735</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1995802363044868</v>
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2356482292435068</v>
       </c>
     </row>
     <row r="24">
@@ -933,7 +1004,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1042209776396423</v>
+        <v>0.3688972325258211</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -941,7 +1012,10 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2026068609408686</v>
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2412067158224415</v>
       </c>
     </row>
     <row r="25">
@@ -951,25 +1025,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1065634717375542</v>
+        <v>0.3736113341468144</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007322077872722325</v>
+        <v>0.007313316050093838</v>
       </c>
       <c r="D25" t="n">
-        <v>25.87559226569</v>
+        <v>25.84123354232302</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04632825638865</v>
+        <v>0.04628126262389513</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09217065190357181</v>
+        <v>0.09204472920764924</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1209562915715369</v>
+        <v>0.1207959214061234</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2049493550387804</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2459208174434347</v>
       </c>
     </row>
     <row r="26">
@@ -979,25 +1056,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1078920291343967</v>
+        <v>0.3773789816069465</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007374014222839818</v>
+        <v>0.007350941733117395</v>
       </c>
       <c r="D26" t="n">
-        <v>-111123772321.5228</v>
+        <v>-111098156278.6998</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05614965926113593</v>
+        <v>0.05560065191666532</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09340131711886501</v>
+        <v>0.09320972893068927</v>
       </c>
       <c r="G26" t="n">
-        <v>0.122382741149928</v>
+        <v>0.1221003696615972</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2062779124356229</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2496884649035669</v>
       </c>
     </row>
     <row r="27">
@@ -1007,7 +1087,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1103345163489635</v>
+        <v>0.3844922207227949</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
@@ -1015,7 +1095,10 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.2087203996501898</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2568017040194153</v>
       </c>
     </row>
     <row r="28">
@@ -1025,25 +1108,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1045415050733467</v>
+        <v>0.3890506140705609</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0066833249351691</v>
+        <v>0.006688595696158981</v>
       </c>
       <c r="D28" t="n">
-        <v>22.90784004910377</v>
+        <v>22.92590616901631</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08255517700603007</v>
+        <v>0.08262028361250172</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0914169604953203</v>
+        <v>0.0914890558900327</v>
       </c>
       <c r="G28" t="n">
-        <v>0.117666049651373</v>
+        <v>0.1177588462204986</v>
       </c>
       <c r="H28" t="n">
-        <v>0.202927388374573</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2613600973671812</v>
       </c>
     </row>
     <row r="29">
@@ -1053,25 +1139,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.005583433311098755</v>
+        <v>0.3372918389820468</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0008485499072841625</v>
+        <v>0.001827289879055183</v>
       </c>
       <c r="D29" t="n">
-        <v>1.294361354548581</v>
+        <v>-8.934754169104659</v>
       </c>
       <c r="E29" t="n">
-        <v>0.007992271573822686</v>
+        <v>0.01055620493661972</v>
       </c>
       <c r="F29" t="n">
-        <v>0.003908741157821331</v>
+        <v>0.001894953635821947</v>
       </c>
       <c r="G29" t="n">
-        <v>0.007258125464376035</v>
+        <v>0.009090033990736681</v>
       </c>
       <c r="H29" t="n">
-        <v>0.103969316612325</v>
+        <v>141</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2096013222786672</v>
       </c>
     </row>
   </sheetData>
